--- a/data/Kc11_mc.xlsx
+++ b/data/Kc11_mc.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thmru\github\2026_EstanciaInvestigacion_PTW\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABF44077-73FA-440A-B0E6-AB3646850E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2EBD49-C7BD-4632-8172-403A4BD70C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{D6D7A118-0CFC-4765-AC15-B69F32FCCA4F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{D6D7A118-0CFC-4765-AC15-B69F32FCCA4F}"/>
   </bookViews>
   <sheets>
     <sheet name="machiningdoctor" sheetId="2" r:id="rId1"/>
+    <sheet name="Steel" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">machiningdoctor!$A$1:$L$715</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="982">
   <si>
     <t>Material</t>
   </si>
@@ -2976,12 +2980,24 @@
   </si>
   <si>
     <t>mc</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>sdt</t>
+  </si>
+  <si>
+    <t>min</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.000"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3137,7 +3153,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3183,6 +3199,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -3518,6 +3535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9E1152F-4A3E-4A6B-B236-0A29CBECDCDC}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L715"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
@@ -3579,12 +3597,12 @@
         <v>975</v>
       </c>
       <c r="J2" s="16">
-        <f>AVERAGE(E2:E715)</f>
-        <v>2304.2436974789916</v>
+        <f>AVERAGE(E2:E296)</f>
+        <v>1714.7457627118645</v>
       </c>
       <c r="K2" s="16">
-        <f>AVERAGE(G2:G715)</f>
-        <v>0.23226890756302479</v>
+        <f>AVERAGE(G2:G296)</f>
+        <v>0.2279661016949153</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3643,6 +3661,13 @@
       <c r="G4" s="3">
         <v>0.21</v>
       </c>
+      <c r="I4" t="s">
+        <v>979</v>
+      </c>
+      <c r="J4">
+        <f>MAX(E2:E296)</f>
+        <v>4700</v>
+      </c>
       <c r="L4" s="14"/>
     </row>
     <row r="5" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3714,7 +3739,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>1022</v>
       </c>
@@ -3806,7 +3831,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>1039</v>
       </c>
@@ -3852,7 +3877,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>1043</v>
       </c>
@@ -3892,7 +3917,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>1049</v>
       </c>
@@ -3962,7 +3987,7 @@
       </c>
       <c r="L18" s="14"/>
     </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="4">
         <v>1050</v>
       </c>
@@ -4006,7 +4031,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="4" t="s">
         <v>26</v>
       </c>
@@ -4075,7 +4100,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>1070</v>
       </c>
@@ -4119,7 +4144,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>1080</v>
       </c>
@@ -4186,7 +4211,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="4" t="s">
         <v>36</v>
       </c>
@@ -4207,7 +4232,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>1100</v>
       </c>
@@ -4224,7 +4249,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="4">
         <v>1108</v>
       </c>
@@ -4247,7 +4272,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>1112</v>
       </c>
@@ -4270,7 +4295,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="4">
         <v>1140</v>
       </c>
@@ -4293,7 +4318,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <v>1144</v>
       </c>
@@ -4316,7 +4341,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="4">
         <v>1151</v>
       </c>
@@ -4339,7 +4364,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>42</v>
       </c>
@@ -4360,7 +4385,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="4">
         <v>1213</v>
       </c>
@@ -4383,7 +4408,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <v>1215</v>
       </c>
@@ -4406,7 +4431,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="4" t="s">
         <v>46</v>
       </c>
@@ -4429,7 +4454,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>49</v>
       </c>
@@ -4452,7 +4477,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="4" t="s">
         <v>51</v>
       </c>
@@ -4475,7 +4500,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2" t="s">
         <v>53</v>
       </c>
@@ -4496,7 +4521,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="4">
         <v>1330</v>
       </c>
@@ -4519,7 +4544,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <v>1335</v>
       </c>
@@ -4542,7 +4567,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="4" t="s">
         <v>56</v>
       </c>
@@ -4565,7 +4590,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2" t="s">
         <v>58</v>
       </c>
@@ -4586,7 +4611,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
@@ -4609,7 +4634,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2" t="s">
         <v>62</v>
       </c>
@@ -4632,7 +4657,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="4" t="s">
         <v>66</v>
       </c>
@@ -4653,7 +4678,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>2011</v>
       </c>
@@ -4676,7 +4701,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="4">
         <v>2014</v>
       </c>
@@ -4699,7 +4724,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <v>2017</v>
       </c>
@@ -4722,7 +4747,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="4" t="s">
         <v>71</v>
       </c>
@@ -4739,7 +4764,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>202</v>
       </c>
@@ -4762,7 +4787,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="4">
         <v>2024</v>
       </c>
@@ -4785,7 +4810,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <v>2050</v>
       </c>
@@ -4802,7 +4827,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="4">
         <v>2090</v>
       </c>
@@ -4819,7 +4844,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <v>2091</v>
       </c>
@@ -4836,7 +4861,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="4">
         <v>2094</v>
       </c>
@@ -4853,7 +4878,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <v>2095</v>
       </c>
@@ -4870,7 +4895,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="4">
         <v>2097</v>
       </c>
@@ -4887,7 +4912,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <v>2098</v>
       </c>
@@ -4904,7 +4929,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="4">
         <v>2099</v>
       </c>
@@ -4921,7 +4946,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2" t="s">
         <v>74</v>
       </c>
@@ -4938,7 +4963,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="4" t="s">
         <v>75</v>
       </c>
@@ -4957,7 +4982,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2" t="s">
         <v>77</v>
       </c>
@@ -4978,7 +5003,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="8">
         <v>39985</v>
       </c>
@@ -4997,7 +5022,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <v>2117</v>
       </c>
@@ -5016,7 +5041,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="4">
         <v>215</v>
       </c>
@@ -5033,7 +5058,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <v>2195</v>
       </c>
@@ -5052,7 +5077,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="4">
         <v>2196</v>
       </c>
@@ -5069,7 +5094,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <v>2197</v>
       </c>
@@ -5086,7 +5111,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="4">
         <v>2198</v>
       </c>
@@ -5103,7 +5128,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <v>2199</v>
       </c>
@@ -5120,7 +5145,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="4">
         <v>2218</v>
       </c>
@@ -5141,7 +5166,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <v>2224</v>
       </c>
@@ -5160,7 +5185,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="4">
         <v>2297</v>
       </c>
@@ -5177,7 +5202,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="2" t="s">
         <v>81</v>
       </c>
@@ -5194,7 +5219,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="4">
         <v>2397</v>
       </c>
@@ -5211,7 +5236,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <v>2515</v>
       </c>
@@ -5234,7 +5259,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="4">
         <v>284</v>
       </c>
@@ -5251,7 +5276,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="2">
         <v>3003</v>
       </c>
@@ -5274,7 +5299,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="4">
         <v>3004</v>
       </c>
@@ -5297,7 +5322,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="2">
         <v>3005</v>
       </c>
@@ -5320,7 +5345,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="4">
         <v>301</v>
       </c>
@@ -5343,7 +5368,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2">
         <v>302</v>
       </c>
@@ -5366,7 +5391,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="4">
         <v>303</v>
       </c>
@@ -5389,7 +5414,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="2">
         <v>304</v>
       </c>
@@ -5412,7 +5437,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="4" t="s">
         <v>90</v>
       </c>
@@ -5433,7 +5458,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="2" t="s">
         <v>92</v>
       </c>
@@ -5456,7 +5481,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="4">
         <v>305</v>
       </c>
@@ -5479,7 +5504,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="2">
         <v>309</v>
       </c>
@@ -5502,7 +5527,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="4" t="s">
         <v>97</v>
       </c>
@@ -5525,7 +5550,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="2" t="s">
         <v>99</v>
       </c>
@@ -5546,7 +5571,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="4" t="s">
         <v>101</v>
       </c>
@@ -5569,7 +5594,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="2">
         <v>3103</v>
       </c>
@@ -5592,7 +5617,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="4">
         <v>3105</v>
       </c>
@@ -5611,7 +5636,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="2">
         <v>311</v>
       </c>
@@ -5628,7 +5653,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="4">
         <v>3115</v>
       </c>
@@ -5651,7 +5676,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="2">
         <v>3135</v>
       </c>
@@ -5674,7 +5699,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="4">
         <v>314</v>
       </c>
@@ -5697,7 +5722,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="2">
         <v>315</v>
       </c>
@@ -5714,7 +5739,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="4">
         <v>316</v>
       </c>
@@ -5737,7 +5762,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2" t="s">
         <v>109</v>
       </c>
@@ -5760,7 +5785,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="4" t="s">
         <v>112</v>
       </c>
@@ -5783,7 +5808,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="2" t="s">
         <v>115</v>
       </c>
@@ -5804,7 +5829,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="4" t="s">
         <v>117</v>
       </c>
@@ -5827,7 +5852,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="2" t="s">
         <v>120</v>
       </c>
@@ -5846,7 +5871,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="4" t="s">
         <v>122</v>
       </c>
@@ -5865,7 +5890,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="2">
         <v>317</v>
       </c>
@@ -5888,7 +5913,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="4" t="s">
         <v>125</v>
       </c>
@@ -5911,7 +5936,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="2">
         <v>318</v>
       </c>
@@ -5934,7 +5959,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="4">
         <v>320</v>
       </c>
@@ -5951,7 +5976,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="2">
         <v>321</v>
       </c>
@@ -5974,7 +5999,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="4" t="s">
         <v>130</v>
       </c>
@@ -5993,7 +6018,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="2">
         <v>325</v>
       </c>
@@ -6010,7 +6035,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="4">
         <v>326</v>
       </c>
@@ -6027,7 +6052,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="2">
         <v>329</v>
       </c>
@@ -6050,7 +6075,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="4">
         <v>330</v>
       </c>
@@ -6073,7 +6098,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="2">
         <v>331</v>
       </c>
@@ -6090,7 +6115,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="4">
         <v>332</v>
       </c>
@@ -6107,7 +6132,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="2">
         <v>334</v>
       </c>
@@ -6128,7 +6153,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="4">
         <v>3415</v>
       </c>
@@ -6151,7 +6176,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="2">
         <v>3415</v>
       </c>
@@ -6174,7 +6199,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="4">
         <v>347</v>
       </c>
@@ -6197,7 +6222,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="2">
         <v>348</v>
       </c>
@@ -6218,7 +6243,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="4" t="s">
         <v>139</v>
       </c>
@@ -6235,7 +6260,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="2" t="s">
         <v>140</v>
       </c>
@@ -6256,7 +6281,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="4">
         <v>394</v>
       </c>
@@ -6273,7 +6298,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="2">
         <v>403</v>
       </c>
@@ -6296,7 +6321,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="4">
         <v>4032</v>
       </c>
@@ -6315,7 +6340,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="2" t="s">
         <v>143</v>
       </c>
@@ -6334,7 +6359,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="4" t="s">
         <v>144</v>
       </c>
@@ -6355,7 +6380,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="2">
         <v>405</v>
       </c>
@@ -6378,7 +6403,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="4">
         <v>409</v>
       </c>
@@ -6401,7 +6426,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="2" t="s">
         <v>148</v>
       </c>
@@ -6418,7 +6443,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="4" t="s">
         <v>149</v>
       </c>
@@ -6435,7 +6460,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="2" t="s">
         <v>150</v>
       </c>
@@ -6456,7 +6481,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="4" t="s">
         <v>152</v>
       </c>
@@ -6477,7 +6502,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="2">
         <v>410</v>
       </c>
@@ -6500,7 +6525,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="4" t="s">
         <v>154</v>
       </c>
@@ -6517,7 +6542,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="2">
         <v>4130</v>
       </c>
@@ -6540,7 +6565,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="4">
         <v>4137</v>
       </c>
@@ -6563,7 +6588,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="2">
         <v>4140</v>
       </c>
@@ -6586,7 +6611,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="4">
         <v>4142</v>
       </c>
@@ -6609,7 +6634,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="2">
         <v>4150</v>
       </c>
@@ -6632,7 +6657,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="4">
         <v>416</v>
       </c>
@@ -6655,7 +6680,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="2">
         <v>420</v>
       </c>
@@ -6678,7 +6703,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="4" t="s">
         <v>162</v>
       </c>
@@ -6701,7 +6726,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="2">
         <v>425</v>
       </c>
@@ -6718,7 +6743,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="4">
         <v>429</v>
       </c>
@@ -6737,7 +6762,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="2">
         <v>430</v>
       </c>
@@ -6760,7 +6785,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="4" t="s">
         <v>165</v>
       </c>
@@ -6783,7 +6808,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="2">
         <v>431</v>
       </c>
@@ -6806,7 +6831,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="4" t="s">
         <v>168</v>
       </c>
@@ -6829,7 +6854,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="2">
         <v>433</v>
       </c>
@@ -6846,7 +6871,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="4">
         <v>434</v>
       </c>
@@ -6869,7 +6894,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="2">
         <v>4340</v>
       </c>
@@ -6892,7 +6917,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="4" t="s">
         <v>172</v>
       </c>
@@ -6909,7 +6934,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="2" t="s">
         <v>173</v>
       </c>
@@ -6926,7 +6951,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="4" t="s">
         <v>174</v>
       </c>
@@ -6949,7 +6974,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="2" t="s">
         <v>176</v>
       </c>
@@ -6972,7 +6997,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="4">
         <v>441</v>
       </c>
@@ -6989,7 +7014,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="2" t="s">
         <v>178</v>
       </c>
@@ -7006,7 +7031,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="4">
         <v>4419</v>
       </c>
@@ -7029,7 +7054,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="2">
         <v>444</v>
       </c>
@@ -7050,7 +7075,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="4">
         <v>446</v>
       </c>
@@ -7073,7 +7098,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="2">
         <v>452</v>
       </c>
@@ -7090,7 +7115,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="4">
         <v>4520</v>
       </c>
@@ -7109,7 +7134,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="2">
         <v>455</v>
       </c>
@@ -7128,7 +7153,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="4" t="s">
         <v>181</v>
       </c>
@@ -7151,7 +7176,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="2">
         <v>500</v>
       </c>
@@ -7168,7 +7193,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="4">
         <v>5005</v>
       </c>
@@ -7191,7 +7216,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="2">
         <v>5015</v>
       </c>
@@ -7214,7 +7239,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="4">
         <v>5045</v>
       </c>
@@ -7237,7 +7262,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="2">
         <v>5052</v>
       </c>
@@ -7260,7 +7285,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="4">
         <v>5056</v>
       </c>
@@ -7283,7 +7308,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="2">
         <v>5083</v>
       </c>
@@ -7306,7 +7331,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="4">
         <v>5086</v>
       </c>
@@ -7329,7 +7354,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="2">
         <v>5115</v>
       </c>
@@ -7375,7 +7400,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="2">
         <v>5130</v>
       </c>
@@ -7398,7 +7423,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="4">
         <v>5132</v>
       </c>
@@ -7421,7 +7446,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="2">
         <v>5135</v>
       </c>
@@ -7444,7 +7469,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="4">
         <v>5140</v>
       </c>
@@ -7467,7 +7492,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="2">
         <v>5140</v>
       </c>
@@ -7490,7 +7515,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="4">
         <v>5154</v>
       </c>
@@ -7513,7 +7538,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="2">
         <v>5155</v>
       </c>
@@ -7536,7 +7561,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="4">
         <v>521</v>
       </c>
@@ -7553,7 +7578,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="2">
         <v>52100</v>
       </c>
@@ -7576,7 +7601,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="4">
         <v>5251</v>
       </c>
@@ -7599,7 +7624,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="2">
         <v>5454</v>
       </c>
@@ -7622,7 +7647,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="4" t="s">
         <v>202</v>
       </c>
@@ -7639,7 +7664,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="2" t="s">
         <v>203</v>
       </c>
@@ -7660,7 +7685,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="4" t="s">
         <v>205</v>
       </c>
@@ -7677,7 +7702,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="2">
         <v>5657</v>
       </c>
@@ -7698,7 +7723,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="4">
         <v>5754</v>
       </c>
@@ -7721,7 +7746,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="2" t="s">
         <v>208</v>
       </c>
@@ -7742,7 +7767,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="4">
         <v>600</v>
       </c>
@@ -7759,7 +7784,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="2">
         <v>6061</v>
       </c>
@@ -7782,7 +7807,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="4">
         <v>6063</v>
       </c>
@@ -7805,7 +7830,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="2">
         <v>6070</v>
       </c>
@@ -7824,7 +7849,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="4" t="s">
         <v>211</v>
       </c>
@@ -7841,7 +7866,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="2">
         <v>610</v>
       </c>
@@ -7858,7 +7883,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="4">
         <v>611</v>
       </c>
@@ -7875,7 +7900,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="2">
         <v>6150</v>
       </c>
@@ -7898,7 +7923,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="4">
         <v>6151</v>
       </c>
@@ -7917,7 +7942,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="2">
         <v>6262</v>
       </c>
@@ -7936,7 +7961,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="4">
         <v>6351</v>
       </c>
@@ -7959,7 +7984,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="2">
         <v>6463</v>
       </c>
@@ -7982,7 +8007,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="4" t="s">
         <v>215</v>
       </c>
@@ -8005,7 +8030,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="2" t="s">
         <v>217</v>
       </c>
@@ -8028,7 +8053,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="4">
         <v>7001</v>
       </c>
@@ -8047,7 +8072,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="2">
         <v>7003</v>
       </c>
@@ -8066,7 +8091,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="4">
         <v>7020</v>
       </c>
@@ -8089,7 +8114,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="2">
         <v>7022</v>
       </c>
@@ -8112,7 +8137,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="4">
         <v>7050</v>
       </c>
@@ -8131,7 +8156,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="2">
         <v>7075</v>
       </c>
@@ -8154,7 +8179,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="4" t="s">
         <v>222</v>
       </c>
@@ -8171,7 +8196,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="2">
         <v>7175</v>
       </c>
@@ -8190,7 +8215,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="4">
         <v>7178</v>
       </c>
@@ -8209,7 +8234,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="2">
         <v>7475</v>
       </c>
@@ -8228,7 +8253,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="4" t="s">
         <v>223</v>
       </c>
@@ -8249,7 +8274,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="2">
         <v>8017</v>
       </c>
@@ -8268,7 +8293,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="4">
         <v>8024</v>
       </c>
@@ -8285,7 +8310,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="2">
         <v>8090</v>
       </c>
@@ -8302,7 +8327,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="4">
         <v>8091</v>
       </c>
@@ -8319,7 +8344,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="2">
         <v>8093</v>
       </c>
@@ -8336,7 +8361,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="4">
         <v>8620</v>
       </c>
@@ -8359,7 +8384,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="2">
         <v>8630</v>
       </c>
@@ -8382,7 +8407,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="4">
         <v>8740</v>
       </c>
@@ -8405,7 +8430,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="2" t="s">
         <v>227</v>
       </c>
@@ -8426,7 +8451,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="4" t="s">
         <v>229</v>
       </c>
@@ -8447,7 +8472,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="2">
         <v>9255</v>
       </c>
@@ -8470,7 +8495,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="4">
         <v>9262</v>
       </c>
@@ -8493,7 +8518,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="2">
         <v>9310</v>
       </c>
@@ -8516,7 +8541,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="4">
         <v>9840</v>
       </c>
@@ -8539,7 +8564,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="2" t="s">
         <v>235</v>
       </c>
@@ -8562,7 +8587,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="4" t="s">
         <v>238</v>
       </c>
@@ -8600,7 +8625,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="4" t="s">
         <v>241</v>
       </c>
@@ -8619,7 +8644,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="2" t="s">
         <v>243</v>
       </c>
@@ -8642,7 +8667,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="4" t="s">
         <v>246</v>
       </c>
@@ -8665,7 +8690,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="2" t="s">
         <v>246</v>
       </c>
@@ -8688,7 +8713,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="4" t="s">
         <v>251</v>
       </c>
@@ -8711,7 +8736,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="2" t="s">
         <v>253</v>
       </c>
@@ -8734,7 +8759,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="4" t="s">
         <v>255</v>
       </c>
@@ -8757,7 +8782,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="2" t="s">
         <v>258</v>
       </c>
@@ -8774,7 +8799,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="4" t="s">
         <v>259</v>
       </c>
@@ -8791,7 +8816,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="2" t="s">
         <v>260</v>
       </c>
@@ -8814,7 +8839,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="4" t="s">
         <v>262</v>
       </c>
@@ -8835,7 +8860,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="2" t="s">
         <v>264</v>
       </c>
@@ -8854,7 +8879,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="4" t="s">
         <v>266</v>
       </c>
@@ -8875,7 +8900,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="2" t="s">
         <v>268</v>
       </c>
@@ -8896,7 +8921,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="4" t="s">
         <v>270</v>
       </c>
@@ -8913,7 +8938,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="2" t="s">
         <v>271</v>
       </c>
@@ -8936,7 +8961,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="4" t="s">
         <v>274</v>
       </c>
@@ -8980,7 +9005,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="259" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="4" t="s">
         <v>278</v>
       </c>
@@ -9003,7 +9028,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="2" t="s">
         <v>281</v>
       </c>
@@ -9026,7 +9051,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="4" t="s">
         <v>284</v>
       </c>
@@ -9045,7 +9070,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="2" t="s">
         <v>285</v>
       </c>
@@ -9064,7 +9089,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="263" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="4" t="s">
         <v>287</v>
       </c>
@@ -9087,7 +9112,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="264" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="2" t="s">
         <v>290</v>
       </c>
@@ -9110,7 +9135,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="265" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="4" t="s">
         <v>290</v>
       </c>
@@ -9133,7 +9158,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="266" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="2" t="s">
         <v>290</v>
       </c>
@@ -9156,7 +9181,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="4" t="s">
         <v>297</v>
       </c>
@@ -9179,7 +9204,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="2" t="s">
         <v>300</v>
       </c>
@@ -9202,7 +9227,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="4" t="s">
         <v>303</v>
       </c>
@@ -9219,7 +9244,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="270" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="2" t="s">
         <v>304</v>
       </c>
@@ -9265,7 +9290,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="272" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A272" s="2" t="s">
         <v>310</v>
       </c>
@@ -9284,7 +9309,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A273" s="4" t="s">
         <v>311</v>
       </c>
@@ -9330,7 +9355,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="275" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A275" s="4" t="s">
         <v>317</v>
       </c>
@@ -9349,7 +9374,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="276" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A276" s="2" t="s">
         <v>318</v>
       </c>
@@ -9370,7 +9395,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A277" s="4" t="s">
         <v>320</v>
       </c>
@@ -9393,7 +9418,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="278" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="2" t="s">
         <v>322</v>
       </c>
@@ -9412,7 +9437,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A279" s="4" t="s">
         <v>324</v>
       </c>
@@ -9429,7 +9454,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A280" s="2" t="s">
         <v>325</v>
       </c>
@@ -9446,7 +9471,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A281" s="4" t="s">
         <v>326</v>
       </c>
@@ -9463,7 +9488,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A282" s="2" t="s">
         <v>327</v>
       </c>
@@ -9482,7 +9507,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A283" s="4" t="s">
         <v>329</v>
       </c>
@@ -9499,7 +9524,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A284" s="2" t="s">
         <v>330</v>
       </c>
@@ -9516,7 +9541,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A285" s="4" t="s">
         <v>331</v>
       </c>
@@ -9533,7 +9558,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="2" t="s">
         <v>332</v>
       </c>
@@ -9550,7 +9575,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A287" s="4" t="s">
         <v>333</v>
       </c>
@@ -9567,7 +9592,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A288" s="2" t="s">
         <v>334</v>
       </c>
@@ -9584,7 +9609,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A289" s="4" t="s">
         <v>335</v>
       </c>
@@ -9603,7 +9628,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="290" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A290" s="2" t="s">
         <v>337</v>
       </c>
@@ -9620,7 +9645,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="291" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="4" t="s">
         <v>338</v>
       </c>
@@ -9643,7 +9668,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="292" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A292" s="2" t="s">
         <v>340</v>
       </c>
@@ -9666,7 +9691,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="293" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A293" s="4" t="s">
         <v>342</v>
       </c>
@@ -9687,7 +9712,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A294" s="2" t="s">
         <v>345</v>
       </c>
@@ -9710,7 +9735,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A295" s="4" t="s">
         <v>347</v>
       </c>
@@ -9756,7 +9781,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="297" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A297" s="4" t="s">
         <v>350</v>
       </c>
@@ -9779,7 +9804,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="298" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A298" s="2" t="s">
         <v>352</v>
       </c>
@@ -9802,7 +9827,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A299" s="4" t="s">
         <v>354</v>
       </c>
@@ -9825,7 +9850,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="300" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A300" s="2" t="s">
         <v>356</v>
       </c>
@@ -9848,7 +9873,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A301" s="4" t="s">
         <v>358</v>
       </c>
@@ -9871,7 +9896,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A302" s="2" t="s">
         <v>358</v>
       </c>
@@ -9894,7 +9919,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="303" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A303" s="4" t="s">
         <v>361</v>
       </c>
@@ -9917,7 +9942,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="304" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A304" s="2" t="s">
         <v>363</v>
       </c>
@@ -9940,7 +9965,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="305" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A305" s="4" t="s">
         <v>365</v>
       </c>
@@ -9963,7 +9988,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A306" s="2" t="s">
         <v>367</v>
       </c>
@@ -9986,7 +10011,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A307" s="4" t="s">
         <v>369</v>
       </c>
@@ -10009,7 +10034,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A308" s="2" t="s">
         <v>371</v>
       </c>
@@ -10032,7 +10057,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A309" s="4" t="s">
         <v>373</v>
       </c>
@@ -10055,7 +10080,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="310" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A310" s="2" t="s">
         <v>375</v>
       </c>
@@ -10074,7 +10099,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="311" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A311" s="4" t="s">
         <v>377</v>
       </c>
@@ -10095,7 +10120,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A312" s="2" t="s">
         <v>378</v>
       </c>
@@ -10118,7 +10143,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A313" s="4" t="s">
         <v>380</v>
       </c>
@@ -10141,7 +10166,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A314" s="2" t="s">
         <v>382</v>
       </c>
@@ -10164,7 +10189,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="315" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A315" s="4" t="s">
         <v>384</v>
       </c>
@@ -10181,7 +10206,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="316" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A316" s="2" t="s">
         <v>385</v>
       </c>
@@ -10200,7 +10225,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="317" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A317" s="4" t="s">
         <v>386</v>
       </c>
@@ -10219,7 +10244,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A318" s="2" t="s">
         <v>388</v>
       </c>
@@ -10238,7 +10263,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A319" s="4" t="s">
         <v>390</v>
       </c>
@@ -10255,7 +10280,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="320" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A320" s="2" t="s">
         <v>391</v>
       </c>
@@ -10272,7 +10297,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="321" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A321" s="4" t="s">
         <v>392</v>
       </c>
@@ -10295,7 +10320,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="322" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A322" s="2" t="s">
         <v>395</v>
       </c>
@@ -10318,7 +10343,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A323" s="4" t="s">
         <v>398</v>
       </c>
@@ -10335,7 +10360,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A324" s="2" t="s">
         <v>399</v>
       </c>
@@ -10358,7 +10383,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A325" s="4" t="s">
         <v>402</v>
       </c>
@@ -10381,7 +10406,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="326" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A326" s="2" t="s">
         <v>405</v>
       </c>
@@ -10398,7 +10423,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="327" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A327" s="4" t="s">
         <v>406</v>
       </c>
@@ -10415,7 +10440,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A328" s="2" t="s">
         <v>407</v>
       </c>
@@ -10432,7 +10457,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A329" s="4" t="s">
         <v>408</v>
       </c>
@@ -10451,7 +10476,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="330" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A330" s="2" t="s">
         <v>410</v>
       </c>
@@ -10470,7 +10495,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="331" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A331" s="4" t="s">
         <v>412</v>
       </c>
@@ -10491,7 +10516,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="332" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A332" s="2" t="s">
         <v>413</v>
       </c>
@@ -10514,7 +10539,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A333" s="4" t="s">
         <v>415</v>
       </c>
@@ -10533,7 +10558,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="334" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A334" s="2" t="s">
         <v>417</v>
       </c>
@@ -10550,7 +10575,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A335" s="4" t="s">
         <v>418</v>
       </c>
@@ -10567,7 +10592,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="336" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A336" s="2" t="s">
         <v>419</v>
       </c>
@@ -10584,7 +10609,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A337" s="4" t="s">
         <v>420</v>
       </c>
@@ -10605,7 +10630,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="338" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A338" s="2" t="s">
         <v>421</v>
       </c>
@@ -10628,7 +10653,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="339" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A339" s="4" t="s">
         <v>423</v>
       </c>
@@ -10651,7 +10676,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A340" s="2" t="s">
         <v>425</v>
       </c>
@@ -10674,7 +10699,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A341" s="4" t="s">
         <v>427</v>
       </c>
@@ -10697,7 +10722,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="342" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A342" s="2" t="s">
         <v>429</v>
       </c>
@@ -10720,7 +10745,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="343" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A343" s="4" t="s">
         <v>431</v>
       </c>
@@ -10743,7 +10768,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A344" s="2" t="s">
         <v>433</v>
       </c>
@@ -10766,7 +10791,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="345" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A345" s="4" t="s">
         <v>435</v>
       </c>
@@ -10789,7 +10814,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="346" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A346" s="2" t="s">
         <v>438</v>
       </c>
@@ -10810,7 +10835,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A347" s="4" t="s">
         <v>439</v>
       </c>
@@ -10833,7 +10858,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A348" s="2" t="s">
         <v>437</v>
       </c>
@@ -10850,7 +10875,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A349" s="4" t="s">
         <v>441</v>
       </c>
@@ -10873,7 +10898,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A350" s="2" t="s">
         <v>443</v>
       </c>
@@ -10896,7 +10921,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A351" s="4" t="s">
         <v>445</v>
       </c>
@@ -10919,7 +10944,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="2" t="s">
         <v>447</v>
       </c>
@@ -10942,7 +10967,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="353" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A353" s="4" t="s">
         <v>449</v>
       </c>
@@ -10965,7 +10990,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A354" s="2" t="s">
         <v>451</v>
       </c>
@@ -10988,7 +11013,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A355" s="4" t="s">
         <v>453</v>
       </c>
@@ -11011,7 +11036,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="356" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="2" t="s">
         <v>456</v>
       </c>
@@ -11034,7 +11059,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="357" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A357" s="4" t="s">
         <v>458</v>
       </c>
@@ -11057,7 +11082,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A358" s="2" t="s">
         <v>461</v>
       </c>
@@ -11080,7 +11105,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A359" s="4" t="s">
         <v>464</v>
       </c>
@@ -11101,7 +11126,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A360" s="2" t="s">
         <v>465</v>
       </c>
@@ -11122,7 +11147,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="361" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A361" s="4" t="s">
         <v>466</v>
       </c>
@@ -11145,7 +11170,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="362" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A362" s="2" t="s">
         <v>469</v>
       </c>
@@ -11168,7 +11193,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="363" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="4" t="s">
         <v>472</v>
       </c>
@@ -11189,7 +11214,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="364" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A364" s="2" t="s">
         <v>473</v>
       </c>
@@ -11210,7 +11235,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="365" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A365" s="4" t="s">
         <v>474</v>
       </c>
@@ -11231,7 +11256,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="366" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A366" s="2" t="s">
         <v>475</v>
       </c>
@@ -11248,7 +11273,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="367" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A367" s="4" t="s">
         <v>476</v>
       </c>
@@ -11265,7 +11290,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="368" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A368" s="2" t="s">
         <v>477</v>
       </c>
@@ -11282,7 +11307,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="369" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A369" s="4" t="s">
         <v>478</v>
       </c>
@@ -11299,7 +11324,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="370" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A370" s="2" t="s">
         <v>479</v>
       </c>
@@ -11318,7 +11343,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="371" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A371" s="4" t="s">
         <v>481</v>
       </c>
@@ -11337,7 +11362,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="372" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A372" s="2" t="s">
         <v>483</v>
       </c>
@@ -11356,7 +11381,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="373" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A373" s="4" t="s">
         <v>484</v>
       </c>
@@ -11379,7 +11404,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A374" s="2" t="s">
         <v>485</v>
       </c>
@@ -11398,7 +11423,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="375" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A375" s="4" t="s">
         <v>486</v>
       </c>
@@ -11415,7 +11440,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="376" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A376" s="2" t="s">
         <v>487</v>
       </c>
@@ -11438,7 +11463,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="377" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A377" s="4" t="s">
         <v>488</v>
       </c>
@@ -11461,7 +11486,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="378" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A378" s="2" t="s">
         <v>490</v>
       </c>
@@ -11482,7 +11507,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="379" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A379" s="4" t="s">
         <v>491</v>
       </c>
@@ -11503,7 +11528,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="380" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A380" s="2" t="s">
         <v>492</v>
       </c>
@@ -11524,7 +11549,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="381" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A381" s="4" t="s">
         <v>493</v>
       </c>
@@ -11547,7 +11572,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="382" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A382" s="2" t="s">
         <v>493</v>
       </c>
@@ -11564,7 +11589,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="383" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A383" s="4" t="s">
         <v>495</v>
       </c>
@@ -11587,7 +11612,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="384" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A384" s="2" t="s">
         <v>497</v>
       </c>
@@ -11610,7 +11635,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="385" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A385" s="4" t="s">
         <v>497</v>
       </c>
@@ -11627,7 +11652,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="386" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A386" s="2" t="s">
         <v>499</v>
       </c>
@@ -11644,7 +11669,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="387" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A387" s="4" t="s">
         <v>500</v>
       </c>
@@ -11667,7 +11692,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="388" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A388" s="2" t="s">
         <v>502</v>
       </c>
@@ -11684,7 +11709,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="389" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A389" s="4" t="s">
         <v>503</v>
       </c>
@@ -11707,7 +11732,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="390" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A390" s="2" t="s">
         <v>503</v>
       </c>
@@ -11724,7 +11749,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="391" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A391" s="4" t="s">
         <v>505</v>
       </c>
@@ -11741,7 +11766,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="392" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A392" s="2" t="s">
         <v>506</v>
       </c>
@@ -11758,7 +11783,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="393" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A393" s="4" t="s">
         <v>507</v>
       </c>
@@ -11775,7 +11800,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="394" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A394" s="2" t="s">
         <v>508</v>
       </c>
@@ -11792,7 +11817,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="395" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A395" s="4" t="s">
         <v>509</v>
       </c>
@@ -11809,7 +11834,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="396" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A396" s="2" t="s">
         <v>510</v>
       </c>
@@ -11826,7 +11851,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="397" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A397" s="4" t="s">
         <v>511</v>
       </c>
@@ -11843,7 +11868,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="398" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A398" s="2" t="s">
         <v>512</v>
       </c>
@@ -11866,7 +11891,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="399" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A399" s="4" t="s">
         <v>515</v>
       </c>
@@ -11883,7 +11908,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="400" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A400" s="2" t="s">
         <v>516</v>
       </c>
@@ -11900,7 +11925,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="401" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A401" s="4" t="s">
         <v>517</v>
       </c>
@@ -11921,7 +11946,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="402" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A402" s="2" t="s">
         <v>519</v>
       </c>
@@ -11938,7 +11963,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A403" s="4" t="s">
         <v>520</v>
       </c>
@@ -11955,7 +11980,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="404" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A404" s="2" t="s">
         <v>521</v>
       </c>
@@ -11974,7 +11999,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="405" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A405" s="4" t="s">
         <v>522</v>
       </c>
@@ -11991,7 +12016,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A406" s="2" t="s">
         <v>523</v>
       </c>
@@ -12008,7 +12033,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="407" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A407" s="4" t="s">
         <v>524</v>
       </c>
@@ -12025,7 +12050,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="408" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A408" s="2" t="s">
         <v>525</v>
       </c>
@@ -12042,7 +12067,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="409" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A409" s="4" t="s">
         <v>526</v>
       </c>
@@ -12065,7 +12090,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="410" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A410" s="2" t="s">
         <v>528</v>
       </c>
@@ -12084,7 +12109,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="411" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A411" s="4" t="s">
         <v>529</v>
       </c>
@@ -12105,7 +12130,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A412" s="2" t="s">
         <v>531</v>
       </c>
@@ -12122,7 +12147,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="413" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A413" s="4" t="s">
         <v>532</v>
       </c>
@@ -12143,7 +12168,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="414" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A414" s="2" t="s">
         <v>534</v>
       </c>
@@ -12166,7 +12191,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A415" s="4" t="s">
         <v>536</v>
       </c>
@@ -12187,7 +12212,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="416" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A416" s="2" t="s">
         <v>537</v>
       </c>
@@ -12210,7 +12235,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="417" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A417" s="4" t="s">
         <v>540</v>
       </c>
@@ -12231,7 +12256,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="418" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A418" s="2" t="s">
         <v>542</v>
       </c>
@@ -12248,7 +12273,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="419" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A419" s="4" t="s">
         <v>543</v>
       </c>
@@ -12269,7 +12294,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="420" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A420" s="2" t="s">
         <v>544</v>
       </c>
@@ -12292,7 +12317,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="421" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A421" s="4" t="s">
         <v>546</v>
       </c>
@@ -12313,7 +12338,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="422" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A422" s="2" t="s">
         <v>549</v>
       </c>
@@ -12334,7 +12359,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A423" s="4" t="s">
         <v>552</v>
       </c>
@@ -12355,7 +12380,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="424" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A424" s="2" t="s">
         <v>554</v>
       </c>
@@ -12376,7 +12401,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="425" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A425" s="4" t="s">
         <v>557</v>
       </c>
@@ -12395,7 +12420,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="426" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A426" s="2" t="s">
         <v>559</v>
       </c>
@@ -12418,7 +12443,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A427" s="4" t="s">
         <v>561</v>
       </c>
@@ -12441,7 +12466,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A428" s="2" t="s">
         <v>564</v>
       </c>
@@ -12464,7 +12489,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="429" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A429" s="4" t="s">
         <v>566</v>
       </c>
@@ -12485,7 +12510,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="430" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A430" s="2" t="s">
         <v>567</v>
       </c>
@@ -12506,7 +12531,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="431" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A431" s="4" t="s">
         <v>570</v>
       </c>
@@ -12529,7 +12554,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="432" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="2" t="s">
         <v>572</v>
       </c>
@@ -12546,7 +12571,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="433" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A433" s="4" t="s">
         <v>573</v>
       </c>
@@ -12563,7 +12588,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="434" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A434" s="2" t="s">
         <v>574</v>
       </c>
@@ -12580,7 +12605,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="435" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A435" s="4" t="s">
         <v>575</v>
       </c>
@@ -12603,7 +12628,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="436" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A436" s="2" t="s">
         <v>578</v>
       </c>
@@ -12626,7 +12651,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="437" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A437" s="4" t="s">
         <v>580</v>
       </c>
@@ -12645,7 +12670,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="438" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A438" s="2" t="s">
         <v>582</v>
       </c>
@@ -12662,7 +12687,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="439" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A439" s="4" t="s">
         <v>583</v>
       </c>
@@ -12681,7 +12706,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="440" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A440" s="2" t="s">
         <v>585</v>
       </c>
@@ -12698,7 +12723,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="441" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A441" s="4" t="s">
         <v>586</v>
       </c>
@@ -12715,7 +12740,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="442" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A442" s="2" t="s">
         <v>587</v>
       </c>
@@ -12734,7 +12759,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="443" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A443" s="4" t="s">
         <v>589</v>
       </c>
@@ -12751,7 +12776,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="444" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A444" s="2" t="s">
         <v>590</v>
       </c>
@@ -12774,7 +12799,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="445" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A445" s="4" t="s">
         <v>591</v>
       </c>
@@ -12791,7 +12816,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="446" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A446" s="2" t="s">
         <v>592</v>
       </c>
@@ -12812,7 +12837,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="447" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A447" s="4" t="s">
         <v>593</v>
       </c>
@@ -12829,7 +12854,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="448" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A448" s="2" t="s">
         <v>594</v>
       </c>
@@ -12846,7 +12871,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="449" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A449" s="4" t="s">
         <v>595</v>
       </c>
@@ -12863,7 +12888,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="450" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A450" s="2" t="s">
         <v>596</v>
       </c>
@@ -12880,7 +12905,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="451" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A451" s="4" t="s">
         <v>597</v>
       </c>
@@ -12897,7 +12922,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="452" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A452" s="2" t="s">
         <v>598</v>
       </c>
@@ -12918,7 +12943,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="453" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A453" s="4" t="s">
         <v>600</v>
       </c>
@@ -12935,7 +12960,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="454" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A454" s="2" t="s">
         <v>601</v>
       </c>
@@ -12954,7 +12979,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="455" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="4" t="s">
         <v>602</v>
       </c>
@@ -12977,7 +13002,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="456" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A456" s="2" t="s">
         <v>604</v>
       </c>
@@ -12994,7 +13019,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="457" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A457" s="4" t="s">
         <v>605</v>
       </c>
@@ -13011,7 +13036,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="458" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A458" s="2" t="s">
         <v>606</v>
       </c>
@@ -13028,7 +13053,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="459" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A459" s="4" t="s">
         <v>607</v>
       </c>
@@ -13045,7 +13070,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="460" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A460" s="2" t="s">
         <v>608</v>
       </c>
@@ -13062,7 +13087,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="461" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A461" s="4" t="s">
         <v>609</v>
       </c>
@@ -13081,7 +13106,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="462" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A462" s="2" t="s">
         <v>610</v>
       </c>
@@ -13098,7 +13123,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="463" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A463" s="4" t="s">
         <v>611</v>
       </c>
@@ -13115,7 +13140,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="464" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A464" s="2" t="s">
         <v>612</v>
       </c>
@@ -13134,7 +13159,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="465" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A465" s="4" t="s">
         <v>613</v>
       </c>
@@ -13153,7 +13178,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="466" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="2" t="s">
         <v>615</v>
       </c>
@@ -13176,7 +13201,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="467" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A467" s="4" t="s">
         <v>617</v>
       </c>
@@ -13193,7 +13218,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="468" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A468" s="2" t="s">
         <v>618</v>
       </c>
@@ -13210,7 +13235,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="469" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A469" s="4" t="s">
         <v>619</v>
       </c>
@@ -13227,7 +13252,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="470" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A470" s="2" t="s">
         <v>620</v>
       </c>
@@ -13244,7 +13269,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="471" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A471" s="4" t="s">
         <v>621</v>
       </c>
@@ -13261,7 +13286,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="472" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A472" s="2" t="s">
         <v>622</v>
       </c>
@@ -13282,7 +13307,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="473" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A473" s="4" t="s">
         <v>624</v>
       </c>
@@ -13299,7 +13324,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="474" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A474" s="2" t="s">
         <v>625</v>
       </c>
@@ -13316,7 +13341,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="475" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A475" s="4" t="s">
         <v>626</v>
       </c>
@@ -13333,7 +13358,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="476" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A476" s="2" t="s">
         <v>627</v>
       </c>
@@ -13350,7 +13375,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="477" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A477" s="4" t="s">
         <v>628</v>
       </c>
@@ -13367,7 +13392,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="478" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A478" s="2" t="s">
         <v>629</v>
       </c>
@@ -13384,7 +13409,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="479" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A479" s="4" t="s">
         <v>630</v>
       </c>
@@ -13401,7 +13426,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="480" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A480" s="2" t="s">
         <v>631</v>
       </c>
@@ -13418,7 +13443,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="481" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A481" s="4" t="s">
         <v>632</v>
       </c>
@@ -13435,7 +13460,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="482" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A482" s="2" t="s">
         <v>633</v>
       </c>
@@ -13452,7 +13477,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="483" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A483" s="4" t="s">
         <v>634</v>
       </c>
@@ -13469,7 +13494,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="484" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A484" s="2" t="s">
         <v>635</v>
       </c>
@@ -13486,7 +13511,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="485" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A485" s="4" t="s">
         <v>636</v>
       </c>
@@ -13505,7 +13530,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="486" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A486" s="2" t="s">
         <v>638</v>
       </c>
@@ -13522,7 +13547,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="487" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A487" s="4" t="s">
         <v>639</v>
       </c>
@@ -13539,7 +13564,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="488" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A488" s="2" t="s">
         <v>640</v>
       </c>
@@ -13556,7 +13581,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="489" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A489" s="4" t="s">
         <v>641</v>
       </c>
@@ -13579,7 +13604,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="490" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A490" s="2" t="s">
         <v>642</v>
       </c>
@@ -13596,7 +13621,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="491" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A491" s="4" t="s">
         <v>643</v>
       </c>
@@ -13615,7 +13640,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="492" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A492" s="2" t="s">
         <v>645</v>
       </c>
@@ -13634,7 +13659,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="493" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A493" s="4" t="s">
         <v>647</v>
       </c>
@@ -13653,7 +13678,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="494" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A494" s="2" t="s">
         <v>649</v>
       </c>
@@ -13670,7 +13695,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="495" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A495" s="4" t="s">
         <v>650</v>
       </c>
@@ -13693,7 +13718,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="496" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A496" s="2" t="s">
         <v>652</v>
       </c>
@@ -13710,7 +13735,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="497" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A497" s="4" t="s">
         <v>653</v>
       </c>
@@ -13729,7 +13754,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="498" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A498" s="2" t="s">
         <v>655</v>
       </c>
@@ -13750,7 +13775,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="499" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A499" s="4" t="s">
         <v>657</v>
       </c>
@@ -13767,7 +13792,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="500" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A500" s="2" t="s">
         <v>658</v>
       </c>
@@ -13784,7 +13809,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="501" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A501" s="4" t="s">
         <v>659</v>
       </c>
@@ -13801,7 +13826,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="502" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A502" s="2" t="s">
         <v>660</v>
       </c>
@@ -13824,7 +13849,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="503" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A503" s="4" t="s">
         <v>661</v>
       </c>
@@ -13843,7 +13868,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="504" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A504" s="2" t="s">
         <v>662</v>
       </c>
@@ -13866,7 +13891,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="505" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A505" s="4" t="s">
         <v>663</v>
       </c>
@@ -13889,7 +13914,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="506" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A506" s="2" t="s">
         <v>663</v>
       </c>
@@ -13906,7 +13931,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="507" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A507" s="4" t="s">
         <v>665</v>
       </c>
@@ -13923,7 +13948,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="508" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A508" s="2" t="s">
         <v>666</v>
       </c>
@@ -13940,7 +13965,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="509" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A509" s="4" t="s">
         <v>667</v>
       </c>
@@ -13957,7 +13982,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="510" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A510" s="2" t="s">
         <v>668</v>
       </c>
@@ -13978,7 +14003,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="511" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A511" s="4" t="s">
         <v>670</v>
       </c>
@@ -14001,7 +14026,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="512" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A512" s="2" t="s">
         <v>672</v>
       </c>
@@ -14020,7 +14045,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="513" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A513" s="4" t="s">
         <v>673</v>
       </c>
@@ -14043,7 +14068,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="514" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A514" s="2" t="s">
         <v>675</v>
       </c>
@@ -14060,7 +14085,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="515" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A515" s="4" t="s">
         <v>676</v>
       </c>
@@ -14077,7 +14102,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="516" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A516" s="2" t="s">
         <v>677</v>
       </c>
@@ -14096,7 +14121,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="517" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A517" s="4" t="s">
         <v>679</v>
       </c>
@@ -14115,7 +14140,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="518" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A518" s="2" t="s">
         <v>681</v>
       </c>
@@ -14134,7 +14159,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="519" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A519" s="4" t="s">
         <v>683</v>
       </c>
@@ -14151,7 +14176,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="520" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A520" s="2" t="s">
         <v>684</v>
       </c>
@@ -14170,7 +14195,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="521" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A521" s="4" t="s">
         <v>686</v>
       </c>
@@ -14187,7 +14212,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="522" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A522" s="2" t="s">
         <v>687</v>
       </c>
@@ -14206,7 +14231,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="523" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A523" s="4" t="s">
         <v>689</v>
       </c>
@@ -14225,7 +14250,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="524" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A524" s="2" t="s">
         <v>690</v>
       </c>
@@ -14242,7 +14267,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="525" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A525" s="4" t="s">
         <v>691</v>
       </c>
@@ -14259,7 +14284,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="526" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A526" s="2" t="s">
         <v>692</v>
       </c>
@@ -14278,7 +14303,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="527" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A527" s="4" t="s">
         <v>694</v>
       </c>
@@ -14295,7 +14320,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="528" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A528" s="2" t="s">
         <v>695</v>
       </c>
@@ -14312,7 +14337,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="529" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A529" s="4" t="s">
         <v>696</v>
       </c>
@@ -14329,7 +14354,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="530" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A530" s="2" t="s">
         <v>697</v>
       </c>
@@ -14346,7 +14371,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="531" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A531" s="4" t="s">
         <v>698</v>
       </c>
@@ -14369,7 +14394,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="532" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A532" s="2" t="s">
         <v>700</v>
       </c>
@@ -14392,7 +14417,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="533" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A533" s="4" t="s">
         <v>702</v>
       </c>
@@ -14411,7 +14436,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="534" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A534" s="2" t="s">
         <v>703</v>
       </c>
@@ -14428,7 +14453,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="535" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A535" s="4" t="s">
         <v>704</v>
       </c>
@@ -14445,7 +14470,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="536" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A536" s="2" t="s">
         <v>705</v>
       </c>
@@ -14466,7 +14491,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="537" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A537" s="4" t="s">
         <v>706</v>
       </c>
@@ -14483,7 +14508,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="538" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A538" s="10" t="s">
         <v>707</v>
       </c>
@@ -14504,7 +14529,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="539" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A539" s="4" t="s">
         <v>710</v>
       </c>
@@ -14525,7 +14550,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="540" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A540" s="2" t="s">
         <v>712</v>
       </c>
@@ -14546,7 +14571,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="541" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A541" s="4" t="s">
         <v>715</v>
       </c>
@@ -14563,7 +14588,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="542" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A542" s="2" t="s">
         <v>716</v>
       </c>
@@ -14580,7 +14605,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="543" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A543" s="4" t="s">
         <v>717</v>
       </c>
@@ -14599,7 +14624,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="544" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A544" s="2" t="s">
         <v>719</v>
       </c>
@@ -14616,7 +14641,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="545" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A545" s="4" t="s">
         <v>720</v>
       </c>
@@ -14633,7 +14658,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="546" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A546" s="2" t="s">
         <v>721</v>
       </c>
@@ -14650,7 +14675,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="547" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A547" s="4" t="s">
         <v>722</v>
       </c>
@@ -14671,7 +14696,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="548" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A548" s="2" t="s">
         <v>724</v>
       </c>
@@ -14692,7 +14717,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="549" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A549" s="4" t="s">
         <v>726</v>
       </c>
@@ -14713,7 +14738,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="550" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A550" s="2" t="s">
         <v>728</v>
       </c>
@@ -14734,7 +14759,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="551" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A551" s="4" t="s">
         <v>730</v>
       </c>
@@ -14751,7 +14776,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="552" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A552" s="2" t="s">
         <v>731</v>
       </c>
@@ -14772,7 +14797,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="553" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A553" s="4" t="s">
         <v>732</v>
       </c>
@@ -14795,7 +14820,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="554" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A554" s="2" t="s">
         <v>735</v>
       </c>
@@ -14812,7 +14837,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="555" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A555" s="4" t="s">
         <v>736</v>
       </c>
@@ -14829,7 +14854,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="556" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A556" s="2" t="s">
         <v>737</v>
       </c>
@@ -14848,7 +14873,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="557" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A557" s="4" t="s">
         <v>738</v>
       </c>
@@ -14869,7 +14894,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="558" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A558" s="2" t="s">
         <v>740</v>
       </c>
@@ -14890,7 +14915,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="559" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A559" s="4" t="s">
         <v>741</v>
       </c>
@@ -14911,7 +14936,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="560" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A560" s="2" t="s">
         <v>743</v>
       </c>
@@ -14930,7 +14955,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="561" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A561" s="4" t="s">
         <v>744</v>
       </c>
@@ -14953,7 +14978,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="562" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A562" s="2" t="s">
         <v>747</v>
       </c>
@@ -14970,7 +14995,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="563" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A563" s="4" t="s">
         <v>748</v>
       </c>
@@ -14989,7 +15014,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="564" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A564" s="2" t="s">
         <v>750</v>
       </c>
@@ -15006,7 +15031,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="565" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A565" s="4" t="s">
         <v>751</v>
       </c>
@@ -15023,7 +15048,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="566" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A566" s="2" t="s">
         <v>27</v>
       </c>
@@ -15046,7 +15071,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="567" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A567" s="4" t="s">
         <v>753</v>
       </c>
@@ -15069,7 +15094,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="568" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A568" s="2" t="s">
         <v>755</v>
       </c>
@@ -15092,7 +15117,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="569" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A569" s="4" t="s">
         <v>756</v>
       </c>
@@ -15115,7 +15140,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="570" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A570" s="2" t="s">
         <v>758</v>
       </c>
@@ -15138,7 +15163,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="571" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A571" s="4" t="s">
         <v>760</v>
       </c>
@@ -15161,7 +15186,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="572" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A572" s="2" t="s">
         <v>762</v>
       </c>
@@ -15180,7 +15205,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="573" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A573" s="11" t="s">
         <v>764</v>
       </c>
@@ -15199,7 +15224,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="574" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A574" s="2" t="s">
         <v>766</v>
       </c>
@@ -15218,7 +15243,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="575" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A575" s="4" t="s">
         <v>768</v>
       </c>
@@ -15239,7 +15264,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="576" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A576" s="2" t="s">
         <v>769</v>
       </c>
@@ -15256,7 +15281,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="577" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A577" s="4" t="s">
         <v>770</v>
       </c>
@@ -15273,7 +15298,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="578" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A578" s="2" t="s">
         <v>771</v>
       </c>
@@ -15296,7 +15321,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="579" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A579" s="4" t="s">
         <v>774</v>
       </c>
@@ -15313,7 +15338,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="580" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A580" s="2" t="s">
         <v>775</v>
       </c>
@@ -15330,7 +15355,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="581" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A581" s="4" t="s">
         <v>776</v>
       </c>
@@ -15347,7 +15372,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="582" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A582" s="2" t="s">
         <v>777</v>
       </c>
@@ -15364,7 +15389,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="583" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A583" s="4" t="s">
         <v>778</v>
       </c>
@@ -15383,7 +15408,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="584" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A584" s="2" t="s">
         <v>780</v>
       </c>
@@ -15404,7 +15429,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="585" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A585" s="4" t="s">
         <v>782</v>
       </c>
@@ -15427,7 +15452,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="586" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A586" s="2" t="s">
         <v>784</v>
       </c>
@@ -15450,7 +15475,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="587" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A587" s="4" t="s">
         <v>786</v>
       </c>
@@ -15467,7 +15492,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="588" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A588" s="2" t="s">
         <v>787</v>
       </c>
@@ -15490,7 +15515,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="589" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A589" s="4" t="s">
         <v>789</v>
       </c>
@@ -15509,7 +15534,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="590" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A590" s="2" t="s">
         <v>790</v>
       </c>
@@ -15528,7 +15553,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="591" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A591" s="4" t="s">
         <v>792</v>
       </c>
@@ -15545,7 +15570,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="592" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A592" s="2" t="s">
         <v>793</v>
       </c>
@@ -15564,7 +15589,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="593" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A593" s="4" t="s">
         <v>795</v>
       </c>
@@ -15581,7 +15606,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="594" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A594" s="2" t="s">
         <v>796</v>
       </c>
@@ -15598,7 +15623,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="595" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A595" s="4" t="s">
         <v>797</v>
       </c>
@@ -15615,7 +15640,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="596" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A596" s="2" t="s">
         <v>798</v>
       </c>
@@ -15632,7 +15657,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="597" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A597" s="4" t="s">
         <v>799</v>
       </c>
@@ -15649,7 +15674,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="598" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A598" s="2" t="s">
         <v>800</v>
       </c>
@@ -15666,7 +15691,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="599" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A599" s="4" t="s">
         <v>801</v>
       </c>
@@ -15683,7 +15708,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="600" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A600" s="2" t="s">
         <v>802</v>
       </c>
@@ -15700,7 +15725,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="601" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A601" s="4" t="s">
         <v>803</v>
       </c>
@@ -15717,7 +15742,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="602" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A602" s="2" t="s">
         <v>804</v>
       </c>
@@ -15740,7 +15765,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="603" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A603" s="4" t="s">
         <v>805</v>
       </c>
@@ -15757,7 +15782,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="604" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A604" s="2" t="s">
         <v>806</v>
       </c>
@@ -15774,7 +15799,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="605" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A605" s="4" t="s">
         <v>807</v>
       </c>
@@ -15795,7 +15820,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="606" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A606" s="2" t="s">
         <v>808</v>
       </c>
@@ -15812,7 +15837,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="607" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A607" s="4" t="s">
         <v>809</v>
       </c>
@@ -15829,7 +15854,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="608" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A608" s="2" t="s">
         <v>810</v>
       </c>
@@ -15846,7 +15871,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="609" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A609" s="4" t="s">
         <v>811</v>
       </c>
@@ -15863,7 +15888,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="610" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A610" s="2" t="s">
         <v>812</v>
       </c>
@@ -15880,7 +15905,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="611" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A611" s="4" t="s">
         <v>813</v>
       </c>
@@ -15899,7 +15924,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="612" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A612" s="2" t="s">
         <v>815</v>
       </c>
@@ -15918,7 +15943,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="613" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A613" s="4" t="s">
         <v>817</v>
       </c>
@@ -15935,7 +15960,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="614" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A614" s="2" t="s">
         <v>818</v>
       </c>
@@ -15952,7 +15977,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="615" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A615" s="4" t="s">
         <v>819</v>
       </c>
@@ -15975,7 +16000,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="616" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A616" s="2" t="s">
         <v>821</v>
       </c>
@@ -15998,7 +16023,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="617" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A617" s="4" t="s">
         <v>823</v>
       </c>
@@ -16015,7 +16040,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="618" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A618" s="2" t="s">
         <v>824</v>
       </c>
@@ -16032,7 +16057,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="619" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A619" s="4" t="s">
         <v>825</v>
       </c>
@@ -16049,7 +16074,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="620" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A620" s="2" t="s">
         <v>826</v>
       </c>
@@ -16066,7 +16091,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="621" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A621" s="4" t="s">
         <v>827</v>
       </c>
@@ -16087,7 +16112,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="622" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A622" s="2" t="s">
         <v>829</v>
       </c>
@@ -16104,7 +16129,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="623" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A623" s="4" t="s">
         <v>830</v>
       </c>
@@ -16121,7 +16146,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="624" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A624" s="2" t="s">
         <v>831</v>
       </c>
@@ -16138,7 +16163,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="625" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A625" s="4" t="s">
         <v>832</v>
       </c>
@@ -16157,7 +16182,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="626" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A626" s="2" t="s">
         <v>834</v>
       </c>
@@ -16176,7 +16201,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="627" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A627" s="4" t="s">
         <v>836</v>
       </c>
@@ -16193,7 +16218,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="628" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A628" s="2" t="s">
         <v>837</v>
       </c>
@@ -16210,7 +16235,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="629" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A629" s="4" t="s">
         <v>838</v>
       </c>
@@ -16227,7 +16252,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="630" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A630" s="2" t="s">
         <v>839</v>
       </c>
@@ -16244,7 +16269,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="631" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A631" s="4" t="s">
         <v>840</v>
       </c>
@@ -16261,7 +16286,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="632" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A632" s="2" t="s">
         <v>841</v>
       </c>
@@ -16280,7 +16305,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="633" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A633" s="4" t="s">
         <v>843</v>
       </c>
@@ -16299,7 +16324,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="634" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A634" s="2" t="s">
         <v>845</v>
       </c>
@@ -16316,7 +16341,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="635" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A635" s="4" t="s">
         <v>846</v>
       </c>
@@ -16339,7 +16364,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="636" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A636" s="2" t="s">
         <v>849</v>
       </c>
@@ -16360,7 +16385,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="637" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A637" s="4" t="s">
         <v>851</v>
       </c>
@@ -16377,7 +16402,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="638" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A638" s="2" t="s">
         <v>852</v>
       </c>
@@ -16394,7 +16419,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="639" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A639" s="4" t="s">
         <v>853</v>
       </c>
@@ -16413,7 +16438,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="640" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A640" s="2" t="s">
         <v>854</v>
       </c>
@@ -16430,7 +16455,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="641" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A641" s="4" t="s">
         <v>855</v>
       </c>
@@ -16447,7 +16472,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="642" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A642" s="2" t="s">
         <v>856</v>
       </c>
@@ -16468,7 +16493,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="643" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A643" s="4" t="s">
         <v>859</v>
       </c>
@@ -16487,7 +16512,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="644" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A644" s="2" t="s">
         <v>861</v>
       </c>
@@ -16508,7 +16533,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="645" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A645" s="4" t="s">
         <v>862</v>
       </c>
@@ -16529,7 +16554,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="646" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A646" s="2" t="s">
         <v>863</v>
       </c>
@@ -16546,7 +16571,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="647" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A647" s="4" t="s">
         <v>864</v>
       </c>
@@ -16567,7 +16592,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="648" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A648" s="2" t="s">
         <v>867</v>
       </c>
@@ -16586,7 +16611,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="649" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A649" s="4" t="s">
         <v>869</v>
       </c>
@@ -16605,7 +16630,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="650" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A650" s="2" t="s">
         <v>871</v>
       </c>
@@ -16626,7 +16651,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="651" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A651" s="4" t="s">
         <v>873</v>
       </c>
@@ -16645,7 +16670,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="652" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A652" s="2" t="s">
         <v>875</v>
       </c>
@@ -16666,7 +16691,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="653" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A653" s="4" t="s">
         <v>878</v>
       </c>
@@ -16687,7 +16712,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="654" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A654" s="2" t="s">
         <v>881</v>
       </c>
@@ -16704,7 +16729,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="655" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A655" s="4" t="s">
         <v>882</v>
       </c>
@@ -16725,7 +16750,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="656" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A656" s="2" t="s">
         <v>885</v>
       </c>
@@ -16746,7 +16771,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="657" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A657" s="4" t="s">
         <v>888</v>
       </c>
@@ -16767,7 +16792,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="658" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A658" s="2" t="s">
         <v>891</v>
       </c>
@@ -16788,7 +16813,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="659" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A659" s="4" t="s">
         <v>894</v>
       </c>
@@ -16807,7 +16832,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="660" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A660" s="2" t="s">
         <v>896</v>
       </c>
@@ -16830,7 +16855,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="661" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A661" s="4" t="s">
         <v>899</v>
       </c>
@@ -16847,7 +16872,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="662" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A662" s="2" t="s">
         <v>900</v>
       </c>
@@ -16866,7 +16891,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="663" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A663" s="4" t="s">
         <v>902</v>
       </c>
@@ -16889,7 +16914,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="664" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A664" s="2" t="s">
         <v>904</v>
       </c>
@@ -16906,7 +16931,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="665" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A665" s="4" t="s">
         <v>905</v>
       </c>
@@ -16929,7 +16954,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="666" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A666" s="2" t="s">
         <v>906</v>
       </c>
@@ -16946,7 +16971,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="667" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A667" s="4" t="s">
         <v>907</v>
       </c>
@@ -16963,7 +16988,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="668" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A668" s="2" t="s">
         <v>908</v>
       </c>
@@ -16980,7 +17005,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="669" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A669" s="4" t="s">
         <v>909</v>
       </c>
@@ -16999,7 +17024,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="670" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A670" s="2" t="s">
         <v>910</v>
       </c>
@@ -17018,7 +17043,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="671" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A671" s="4" t="s">
         <v>911</v>
       </c>
@@ -17037,7 +17062,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="672" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A672" s="2" t="s">
         <v>912</v>
       </c>
@@ -17056,7 +17081,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="673" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A673" s="4" t="s">
         <v>914</v>
       </c>
@@ -17075,7 +17100,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="674" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A674" s="2" t="s">
         <v>916</v>
       </c>
@@ -17094,7 +17119,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="675" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A675" s="4" t="s">
         <v>918</v>
       </c>
@@ -17113,7 +17138,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="676" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A676" s="2" t="s">
         <v>920</v>
       </c>
@@ -17134,7 +17159,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="677" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A677" s="4" t="s">
         <v>922</v>
       </c>
@@ -17153,7 +17178,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="678" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A678" s="2" t="s">
         <v>924</v>
       </c>
@@ -17172,7 +17197,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="679" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A679" s="4" t="s">
         <v>926</v>
       </c>
@@ -17191,7 +17216,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="680" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A680" s="2" t="s">
         <v>928</v>
       </c>
@@ -17210,7 +17235,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="681" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A681" s="4" t="s">
         <v>930</v>
       </c>
@@ -17227,7 +17252,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="682" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A682" s="2" t="s">
         <v>931</v>
       </c>
@@ -17250,7 +17275,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="683" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A683" s="4" t="s">
         <v>933</v>
       </c>
@@ -17273,7 +17298,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="684" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A684" s="2" t="s">
         <v>935</v>
       </c>
@@ -17296,7 +17321,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="685" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A685" s="4" t="s">
         <v>937</v>
       </c>
@@ -17315,7 +17340,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="686" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A686" s="2" t="s">
         <v>939</v>
       </c>
@@ -17336,7 +17361,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="687" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A687" s="4" t="s">
         <v>940</v>
       </c>
@@ -17353,7 +17378,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="688" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A688" s="2" t="s">
         <v>941</v>
       </c>
@@ -17370,7 +17395,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="689" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A689" s="4" t="s">
         <v>942</v>
       </c>
@@ -17387,7 +17412,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="690" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A690" s="2" t="s">
         <v>943</v>
       </c>
@@ -17408,7 +17433,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="691" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A691" s="4" t="s">
         <v>944</v>
       </c>
@@ -17429,7 +17454,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="692" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A692" s="2" t="s">
         <v>945</v>
       </c>
@@ -17448,7 +17473,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="693" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A693" s="4" t="s">
         <v>946</v>
       </c>
@@ -17469,7 +17494,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="694" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A694" s="2" t="s">
         <v>947</v>
       </c>
@@ -17488,7 +17513,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="695" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A695" s="4" t="s">
         <v>948</v>
       </c>
@@ -17507,7 +17532,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="696" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A696" s="2" t="s">
         <v>949</v>
       </c>
@@ -17528,7 +17553,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="697" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A697" s="4" t="s">
         <v>952</v>
       </c>
@@ -17547,7 +17572,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="698" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A698" s="2" t="s">
         <v>163</v>
       </c>
@@ -17566,7 +17591,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="699" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A699" s="4" t="s">
         <v>953</v>
       </c>
@@ -17587,7 +17612,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="700" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A700" s="2" t="s">
         <v>954</v>
       </c>
@@ -17606,7 +17631,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="701" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A701" s="4" t="s">
         <v>955</v>
       </c>
@@ -17629,7 +17654,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="702" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A702" s="2" t="s">
         <v>957</v>
       </c>
@@ -17650,7 +17675,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="703" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A703" s="4" t="s">
         <v>958</v>
       </c>
@@ -17671,7 +17696,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="704" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A704" s="2" t="s">
         <v>959</v>
       </c>
@@ -17692,7 +17717,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="705" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A705" s="4" t="s">
         <v>960</v>
       </c>
@@ -17713,7 +17738,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="706" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A706" s="2" t="s">
         <v>961</v>
       </c>
@@ -17732,7 +17757,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="707" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A707" s="4" t="s">
         <v>962</v>
       </c>
@@ -17753,7 +17778,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="708" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A708" s="2" t="s">
         <v>963</v>
       </c>
@@ -17770,7 +17795,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="709" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A709" s="4" t="s">
         <v>964</v>
       </c>
@@ -17789,7 +17814,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="710" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A710" s="2" t="s">
         <v>965</v>
       </c>
@@ -17808,7 +17833,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="711" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A711" s="4" t="s">
         <v>966</v>
       </c>
@@ -17827,7 +17852,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="712" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A712" s="2" t="s">
         <v>967</v>
       </c>
@@ -17846,7 +17871,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="713" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A713" s="4" t="s">
         <v>969</v>
       </c>
@@ -17867,7 +17892,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="714" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A714" s="2" t="s">
         <v>971</v>
       </c>
@@ -17884,7 +17909,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="715" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A715" s="12" t="s">
         <v>972</v>
       </c>
@@ -17906,6 +17931,37 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L715" xr:uid="{F9E1152F-4A3E-4A6B-B236-0A29CBECDCDC}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="C15"/>
+        <filter val="C16E"/>
+        <filter val="C22"/>
+        <filter val="C22-8"/>
+        <filter val="C25"/>
+        <filter val="C35"/>
+        <filter val="C40"/>
+        <filter val="C45"/>
+        <filter val="C60"/>
+        <filter val="Cf53"/>
+        <filter val="Ck10"/>
+        <filter val="Ck101"/>
+        <filter val="Ck25"/>
+        <filter val="Ck35"/>
+        <filter val="Ck50"/>
+        <filter val="Ck55"/>
+        <filter val="Ck67"/>
+        <filter val="Ck75"/>
+        <filter val="Ck85"/>
+        <filter val="St12"/>
+        <filter val="St37"/>
+        <filter val="St37.3"/>
+        <filter val="ST-37-2"/>
+        <filter val="St52-3"/>
+        <filter val="StE355"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="B318" r:id="rId1" display="https://www.machiningdoctor.com/glossary/grade/" xr:uid="{0C4C3611-24A6-4994-AF7F-CA24D496BB00}"/>
     <hyperlink ref="A538" r:id="rId2" display="https://www.machiningdoctor.com/glossary/nickel/" xr:uid="{F4777F70-7C2D-46AC-A673-76BC9BB735DC}"/>
@@ -17914,4 +17970,667 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFA24238-456D-4079-A097-EB6BAB6522D4}">
+  <dimension ref="A1:K26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="10" max="10" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>974</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>977</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1006</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1.0037</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1350</v>
+      </c>
+      <c r="F2" s="3">
+        <v>196</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>975</v>
+      </c>
+      <c r="J2" s="17">
+        <f>AVERAGE(E2:E26)</f>
+        <v>1527</v>
+      </c>
+      <c r="K2" s="17">
+        <f>AVERAGE(G2:G26)</f>
+        <v>0.22360000000000008</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
+        <v>1008</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1008</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1.0201</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1350</v>
+      </c>
+      <c r="F3" s="5">
+        <v>196</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>980</v>
+      </c>
+      <c r="J3" s="17">
+        <f>_xlfn.STDEV.S(E2:E26)</f>
+        <v>164.71566410029132</v>
+      </c>
+      <c r="K3" s="17">
+        <f>_xlfn.STDEV.S(G2:G26)</f>
+        <v>1.3190905958272917E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>1010</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1010</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1.1121000000000001</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1350</v>
+      </c>
+      <c r="F4" s="3">
+        <v>196</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>979</v>
+      </c>
+      <c r="J4" s="17">
+        <f>MAX(E2:E26)</f>
+        <v>1775</v>
+      </c>
+      <c r="K4" s="17">
+        <f>MAX(G2:G26)</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
+        <v>1015</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1015</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1.0401</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1350</v>
+      </c>
+      <c r="F5" s="5">
+        <v>196</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>981</v>
+      </c>
+      <c r="J5" s="17">
+        <f>MIN(E2:E26)</f>
+        <v>1350</v>
+      </c>
+      <c r="K5" s="17">
+        <f>MIN(G2:G26)</f>
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>1018</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1018</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1.1148</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1350</v>
+      </c>
+      <c r="F6" s="3">
+        <v>196</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
+        <v>1020</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1020</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1.0402</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1350</v>
+      </c>
+      <c r="F7" s="5">
+        <v>196</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
+        <v>1025</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1025</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.1157999999999999</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1350</v>
+      </c>
+      <c r="F8" s="5">
+        <v>196</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>1035</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1035</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1.0501</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="3">
+        <v>218</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
+        <v>1035</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1035</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.1183000000000001</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="5">
+        <v>218</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
+        <v>1040</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1040</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1.0510999999999999</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1500</v>
+      </c>
+      <c r="F11" s="5">
+        <v>218</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4">
+        <v>1045</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1045</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.0503</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1500</v>
+      </c>
+      <c r="F12" s="5">
+        <v>218</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4">
+        <v>1049</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.1206</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1500</v>
+      </c>
+      <c r="F13" s="5">
+        <v>218</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>1050</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1050</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1.1213</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F14" s="3">
+        <v>218</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>1055</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1055</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.1203000000000001</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F15" s="3">
+        <v>247</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>1060</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1060</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1.0601</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F16" s="3">
+        <v>247</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4">
+        <v>1070</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1070</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1.1231</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1700</v>
+      </c>
+      <c r="F17" s="5">
+        <v>247</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4">
+        <v>1080</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1080</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.1248</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1700</v>
+      </c>
+      <c r="F18" s="5">
+        <v>247</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4">
+        <v>1086</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1086</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1.1269</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1700</v>
+      </c>
+      <c r="F19" s="5">
+        <v>247</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>1095</v>
+      </c>
+      <c r="B20" s="3">
+        <v>1095</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1.1274</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F20" s="3">
+        <v>247</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4">
+        <v>5120</v>
+      </c>
+      <c r="B21" s="5">
+        <v>5120</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1.0841000000000001</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1775</v>
+      </c>
+      <c r="F21" s="5">
+        <v>257</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3">
+        <v>1775</v>
+      </c>
+      <c r="F22" s="3">
+        <v>257</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1.0117</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1350</v>
+      </c>
+      <c r="F23" s="3">
+        <v>196</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1.0116000000000001</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1775</v>
+      </c>
+      <c r="F24" s="5">
+        <v>257</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1.0562</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1350</v>
+      </c>
+      <c r="F25" s="3">
+        <v>196</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1025</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1.0406</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F26" s="3">
+        <v>218</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0.22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>